--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A45A23F-13C7-4483-9F4F-62A7D531AFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D977CAB7-7C59-4AB4-A591-0F6B1381BC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D977CAB7-7C59-4AB4-A591-0F6B1381BC5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{365A0E79-0BD1-4E1F-8D46-66E93DC31A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{365A0E79-0BD1-4E1F-8D46-66E93DC31A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C17A401E-3C92-4129-902D-9C4BF2401F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -277,15 +277,21 @@
     <t>POL</t>
   </si>
   <si>
+    <t>gen2</t>
+  </si>
+  <si>
+    <t>at grid node - gen2</t>
+  </si>
+  <si>
+    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
+  </si>
+  <si>
     <t>gen1</t>
   </si>
   <si>
     <t>at grid node - gen1</t>
   </si>
   <si>
-    <t>Bioenergy + CCUS,Bioenergy - Large scale unit,CCGT,CCGT + CCS,Coal + CCS,Gas turbine,IGCC,IGCC + CCS,Nuclear large,Oxyfuel + CCS,Steam Coal - SUBCRITICAL,Steam Coal - SUPERCRITICAL,Steam Coal - ULTRASUPERCRITICAL</t>
-  </si>
-  <si>
     <t>gen4</t>
   </si>
   <si>
@@ -296,12 +302,6 @@
   </si>
   <si>
     <t>at grid node - gen0</t>
-  </si>
-  <si>
-    <t>gen2</t>
-  </si>
-  <si>
-    <t>at grid node - gen2</t>
   </si>
   <si>
     <t>gen3</t>
@@ -879,10 +879,10 @@
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J13" t="s">
         <v>90</v>
@@ -929,10 +929,10 @@
         <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="J14" t="s">
         <v>90</v>

--- a/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_syn_5/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_syn_5\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C17A401E-3C92-4129-902D-9C4BF2401F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C99E63A9-17CA-4E3A-A325-1618934B4E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
